--- a/01_Preprocess/03_Quantify/c_data/03_quantify.xlsx
+++ b/01_Preprocess/03_Quantify/c_data/03_quantify.xlsx
@@ -11715,7 +11715,7 @@
     <t>normalized</t>
   </si>
   <si>
-    <t>01_Preprocess/02_Normalization/c_data/DAList_normalized.rds</t>
+    <t>01_Preprocess/02_Normalize/c_data/DAList_normalized.rds</t>
   </si>
   <si>
     <t>39482f6e099d2d703c72e1364ec31471</t>
